--- a/data/processed/harmonization/Physical__Dry_bulk_density/10.15485_2283432/10.15485_2283432_soil_Physical__Dry_bulk_density.xlsx
+++ b/data/processed/harmonization/Physical__Dry_bulk_density/10.15485_2283432/10.15485_2283432_soil_Physical__Dry_bulk_density.xlsx
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>187946:0-20</t>
+          <t>0-20:187946</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>187947:20-40</t>
+          <t>20-40:187947</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -634,12 +634,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>187948:40-60</t>
+          <t>40-60:187948</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>187949:60-100</t>
+          <t>60-100:187949</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>187950:0-20</t>
+          <t>0-20:187950</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>188051:20-40</t>
+          <t>20-40:188051</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>187951:40-60</t>
+          <t>40-60:187951</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>187952:60-100</t>
+          <t>60-100:187952</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>187955:0-20</t>
+          <t>0-20:187955</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>187956:20-40</t>
+          <t>20-40:187956</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>187957:40-60</t>
+          <t>40-60:187957</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>188054:60-100</t>
+          <t>60-100:188054</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>187953:0-20</t>
+          <t>0-20:187953</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>187954:20-40</t>
+          <t>20-40:187954</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>188052:40-60</t>
+          <t>40-60:188052</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>188053:60-100</t>
+          <t>60-100:188053</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>NA:20-40</t>
+          <t>20-40:NA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>NA:20-40</t>
+          <t>20-40:NA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>187946:0-20</t>
+          <t>0-20:187946</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>187947:20-40</t>
+          <t>20-40:187947</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>187948:40-60</t>
+          <t>40-60:187948</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2009,12 +2009,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>187949:60-100</t>
+          <t>60-100:187949</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>187950:0-20</t>
+          <t>0-20:187950</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>188051:20-40</t>
+          <t>20-40:188051</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>187951:40-60</t>
+          <t>40-60:187951</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>187952:60-100</t>
+          <t>60-100:187952</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>187955:0-20</t>
+          <t>0-20:187955</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>187956:20-40</t>
+          <t>20-40:187956</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>187957:40-60</t>
+          <t>40-60:187957</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>188054:60-100</t>
+          <t>60-100:188054</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>187953:0-20</t>
+          <t>0-20:187953</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>187954:20-40</t>
+          <t>20-40:187954</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>188052:40-60</t>
+          <t>40-60:188052</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>188053:60-100</t>
+          <t>60-100:188053</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>NA:20-40</t>
+          <t>20-40:NA</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2999,12 +2999,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>187946:0-20</t>
+          <t>0-20:187946</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>187947:20-40</t>
+          <t>20-40:187947</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>187949:60-100</t>
+          <t>60-100:187949</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>187950:0-20</t>
+          <t>0-20:187950</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>187955:0-20</t>
+          <t>0-20:187955</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>187956:20-40</t>
+          <t>20-40:187956</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>187957:40-60</t>
+          <t>40-60:187957</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>188054:60-100</t>
+          <t>60-100:188054</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>187953:0-20</t>
+          <t>0-20:187953</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>188052:40-60</t>
+          <t>40-60:188052</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>NA:20-40</t>
+          <t>20-40:NA</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>NA:0-20</t>
+          <t>0-20:NA</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3934,12 +3934,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>NA:40-60</t>
+          <t>40-60:NA</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>NA:60-100</t>
+          <t>60-100:NA</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number:depth</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
